--- a/output/pdf_financials_xlsx/VAX.xlsx
+++ b/output/pdf_financials_xlsx/VAX.xlsx
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.017778</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.011344</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>4.6e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1409,13 +1409,13 @@
         <v>-0.147928</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.366415</v>
+        <v>-0.384193</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.525116</v>
+        <v>-0.53646</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.215957</v>
+        <v>-0.216003</v>
       </c>
     </row>
     <row r="28">
@@ -1481,13 +1481,13 @@
         <v>-0.147928</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.366415</v>
+        <v>-0.384193</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.525116</v>
+        <v>-0.53646</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.215957</v>
+        <v>-0.216003</v>
       </c>
     </row>
     <row r="30">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">

--- a/output/pdf_financials_xlsx/VAX.xlsx
+++ b/output/pdf_financials_xlsx/VAX.xlsx
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.00045</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.718568</v>
+        <v>-3.718118</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.447966</v>
@@ -12653,7 +12653,11 @@
           <t>Depreciation of property, plant and equipment (Note 11)</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VAX.xlsx
+++ b/output/pdf_financials_xlsx/VAX.xlsx
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.022818</v>
+        <v>0.049829</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.12737</v>
+        <v>0.200797</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.003682</v>
+        <v>0.06755800000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.010944</v>
+        <v>0.080858</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.00987</v>
+        <v>0.071216</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.009128000000000001</v>
+        <v>0.070266</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.010389</v>
+        <v>0.073353</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.009681</v>
+        <v>0.07746599999999999</v>
       </c>
     </row>
     <row r="8">
@@ -738,28 +738,28 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.022818</v>
+        <v>0.049829</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.12737</v>
+        <v>0.200797</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.003682</v>
+        <v>0.06755800000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.010944</v>
+        <v>0.080858</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.00987</v>
+        <v>0.071216</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.009128000000000001</v>
+        <v>0.070266</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.010389</v>
+        <v>0.073353</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.009681</v>
+        <v>0.07746599999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1877,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.052408</v>
+        <v>0.102408</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.005819</v>
@@ -2165,7 +2165,7 @@
         <v>0.01359</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.018964</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -9055,7 +9055,11 @@
           <t>Rent and office expenses</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
